--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN.xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN.xlsx
@@ -275,7 +275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,6 +384,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
@@ -391,6 +392,9 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -416,6 +420,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -817,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N26"/>
+  <dimension ref="B2:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.796875" customWidth="1" style="3" min="1" max="1"/>
@@ -828,7 +835,7 @@
     <col width="13.59765625" customWidth="1" style="3" min="11" max="12"/>
     <col width="10.296875" customWidth="1" style="3" min="13" max="13"/>
     <col width="36.8984375" customWidth="1" style="3" min="14" max="14"/>
-    <col width="8.796875" customWidth="1" style="3" min="15" max="16384"/>
+    <col width="15" customWidth="1" style="3" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="13.8" customHeight="1" s="35">
@@ -853,7 +860,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ 통계 : 25.04 ~ 26.09 기준 · 국내외 전체 2,139건(글로벌 167건 = JP 99 + US 68) · 26.09.07 갱신</t>
+          <t>※ 통계 : 25.04 ~ 26.09 · 국내외 전체 2,139건(글로벌 167건 = JP 99 + US 68) · 26.09.07 기준</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -872,7 +879,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>※ RD : 표준 기준 ⑤ — 수량·비용 전체 2,139건 / 조회수·참여·CPV·CPE 성과 집계분 2,086건(IMD 2,050 + 바이오힐보 US 36)</t>
+          <t>※ RD : 표준 기준 ⑤ — 수량·비용 전체 2,139건 / 조회수·참여 성과 집계분 2,086건 · 모든 단가는 세금계산서 발행 비용 기준</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -933,6 +940,11 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="O6" s="40" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="12" t="inlineStr">
@@ -995,7 +1007,12 @@
           <t>ROAS</t>
         </is>
       </c>
-      <c r="N7" s="40" t="n"/>
+      <c r="N7" s="41" t="n"/>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>세금계산서</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="39.6" customHeight="1" s="35">
       <c r="B8" s="13" t="inlineStr">
@@ -1003,36 +1020,38 @@
           <t>아이디얼포맨</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="42" t="n">
         <v>737</v>
       </c>
-      <c r="D8" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="41">
+      <c r="D8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="42">
         <f>SUM(C8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="42" t="n">
         <v>17330588</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="42">
         <f>F8/E8</f>
         <v/>
       </c>
-      <c r="H8" s="41" t="n">
-        <v>186345</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="J8" s="41" t="n">
-        <v>1002</v>
-      </c>
-      <c r="K8" s="41" t="n">
+      <c r="H8" s="42" t="n">
+        <v>231083</v>
+      </c>
+      <c r="I8" s="43">
+        <f>O8/F8</f>
+        <v/>
+      </c>
+      <c r="J8" s="42">
+        <f>ROUND(O8/H8,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="42" t="n">
         <v>33768439</v>
       </c>
-      <c r="L8" s="41" t="n">
+      <c r="L8" s="42" t="n">
         <v>102736712</v>
       </c>
       <c r="M8" s="15">
@@ -1045,6 +1064,9 @@
 250%대 ROAS는 300% 이상으로 올라 섬</t>
         </is>
       </c>
+      <c r="O8" s="44" t="n">
+        <v>329997090</v>
+      </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" s="35">
       <c r="B9" s="13" t="inlineStr">
@@ -1052,36 +1074,38 @@
           <t>브링그린</t>
         </is>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="42" t="n">
         <v>313</v>
       </c>
-      <c r="D9" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="41">
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="42">
         <f>SUM(C9:D9)</f>
         <v/>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="42" t="n">
         <v>15535558</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="42">
         <f>F9/E9</f>
         <v/>
       </c>
-      <c r="H9" s="41" t="n">
-        <v>49592</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="J9" s="41" t="n">
-        <v>1337</v>
-      </c>
-      <c r="K9" s="41" t="n">
+      <c r="H9" s="42" t="n">
+        <v>59372</v>
+      </c>
+      <c r="I9" s="43">
+        <f>O9/F9</f>
+        <v/>
+      </c>
+      <c r="J9" s="42">
+        <f>ROUND(O9/H9,0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="42" t="n">
         <v>124304394</v>
       </c>
-      <c r="L9" s="41" t="n">
+      <c r="L9" s="42" t="n">
         <v>729266288</v>
       </c>
       <c r="M9" s="15">
@@ -1093,6 +1117,9 @@
           <t>11개 브랜드 전체 퍼포먼스 광고비 중 44% 집행 → UGC&amp;협력광고 중심 티트리 라인 스케일업 필요</t>
         </is>
       </c>
+      <c r="O9" s="44" t="n">
+        <v>117186968</v>
+      </c>
     </row>
     <row r="10" ht="26.4" customHeight="1" s="35">
       <c r="B10" s="13" t="inlineStr">
@@ -1100,36 +1127,38 @@
           <t>라운드어라운드</t>
         </is>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="42" t="n">
         <v>281</v>
       </c>
-      <c r="D10" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="41">
+      <c r="D10" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="42">
         <f>SUM(C10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="42" t="n">
         <v>2413068</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="42">
         <f>F10/E10</f>
         <v/>
       </c>
-      <c r="H10" s="41" t="n">
-        <v>41731</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>25.51</v>
-      </c>
-      <c r="J10" s="41" t="n">
-        <v>1475</v>
-      </c>
-      <c r="K10" s="41" t="n">
+      <c r="H10" s="42" t="n">
+        <v>47169</v>
+      </c>
+      <c r="I10" s="43">
+        <f>O10/F10</f>
+        <v/>
+      </c>
+      <c r="J10" s="42">
+        <f>ROUND(O10/H10,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="42" t="n">
         <v>133848</v>
       </c>
-      <c r="L10" s="41" t="n">
+      <c r="L10" s="42" t="n">
         <v>348140</v>
       </c>
       <c r="M10" s="15">
@@ -1138,8 +1167,11 @@
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
-          <t>PR키트 진행 등 참여율 1위</t>
-        </is>
+          <t>PR키트 진행 등 참여율 1위(1.95%)</t>
+        </is>
+      </c>
+      <c r="O10" s="44" t="n">
+        <v>108791220</v>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="35">
@@ -1148,36 +1180,38 @@
           <t>바이오힐보 (국내)</t>
         </is>
       </c>
-      <c r="C11" s="41" t="n">
+      <c r="C11" s="42" t="n">
         <v>195</v>
       </c>
-      <c r="D11" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="41">
+      <c r="D11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="42">
         <f>SUM(C11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="42" t="n">
         <v>5440064</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="42">
         <f>F11/E11</f>
         <v/>
       </c>
-      <c r="H11" s="41" t="n">
-        <v>24922</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="J11" s="41" t="n">
-        <v>1521</v>
-      </c>
-      <c r="K11" s="41" t="n">
+      <c r="H11" s="42" t="n">
+        <v>29506</v>
+      </c>
+      <c r="I11" s="43">
+        <f>O11/F11</f>
+        <v/>
+      </c>
+      <c r="J11" s="42">
+        <f>ROUND(O11/H11,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="42" t="n">
         <v>56333229</v>
       </c>
-      <c r="L11" s="41" t="n">
+      <c r="L11" s="42" t="n">
         <v>172219558</v>
       </c>
       <c r="M11" s="15">
@@ -1190,6 +1224,9 @@
 최대 조회수 764,503뷰</t>
         </is>
       </c>
+      <c r="O11" s="44" t="n">
+        <v>66989232</v>
+      </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" s="35">
       <c r="B12" s="13" t="inlineStr">
@@ -1197,36 +1234,38 @@
           <t>바이오힐보 (해외·JP)</t>
         </is>
       </c>
-      <c r="C12" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="41" t="n">
+      <c r="C12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="42">
         <f>SUM(C12:D12)</f>
         <v/>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="42" t="n">
         <v>44255</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="42">
         <f>F12/E12</f>
         <v/>
       </c>
-      <c r="H12" s="41" t="n">
-        <v>29</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="J12" s="41" t="n">
-        <v>57447</v>
-      </c>
-      <c r="K12" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="41" t="n">
+      <c r="H12" s="42" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" s="43">
+        <f>O12/F12</f>
+        <v/>
+      </c>
+      <c r="J12" s="42">
+        <f>ROUND(O12/H12,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="15" t="inlineStr">
@@ -1236,9 +1275,12 @@
       </c>
       <c r="N12" s="16" t="inlineStr">
         <is>
-          <t>25.8~9월 빅빙세일 나노 시딩 테스트
+          <t>26.06 NAD 크림 나노 시딩 테스트
 조회수·참여 모두 저조</t>
         </is>
+      </c>
+      <c r="O12" s="44" t="n">
+        <v>2944636</v>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" s="35">
@@ -1247,36 +1289,38 @@
           <t>바이오힐보 (해외·US)</t>
         </is>
       </c>
-      <c r="C13" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="41" t="n">
+      <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
         <v>68</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="42">
         <f>SUM(C13:D13)</f>
         <v/>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="42" t="n">
         <v>4739117</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="42">
         <f>F13/E13</f>
         <v/>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="42" t="n">
         <v>24134</v>
       </c>
-      <c r="I13" s="42" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="J13" s="41" t="n">
-        <v>1243</v>
-      </c>
-      <c r="K13" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="41" t="n">
+      <c r="I13" s="43">
+        <f>O13/F13</f>
+        <v/>
+      </c>
+      <c r="J13" s="42">
+        <f>ROUND(O13/H13,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="15" t="inlineStr">
@@ -1287,8 +1331,11 @@
       <c r="N13" s="16" t="inlineStr">
         <is>
           <t>68건 중 36건 성과 확보 · 건당 131,642뷰(국내의 4.7배)
-최대 2,954,129뷰 = 전체 1위 / CPV는 청구 기준</t>
-        </is>
+최대 2,954,129뷰 = 전체 1위</t>
+        </is>
+      </c>
+      <c r="O13" s="44" t="n">
+        <v>30000000</v>
       </c>
     </row>
     <row r="14" ht="39.6" customHeight="1" s="35">
@@ -1297,39 +1344,41 @@
           <t>식물나라</t>
         </is>
       </c>
-      <c r="C14" s="41" t="n">
+      <c r="C14" s="42" t="n">
         <v>140</v>
       </c>
-      <c r="D14" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="41">
+      <c r="D14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="42">
         <f>SUM(C14:D14)</f>
         <v/>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F14" s="42" t="n">
         <v>2788821</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="42">
         <f>F14/E14</f>
         <v/>
       </c>
-      <c r="H14" s="41" t="n">
-        <v>20319</v>
-      </c>
-      <c r="I14" s="42" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="J14" s="41" t="n">
-        <v>1599</v>
-      </c>
-      <c r="K14" s="41" t="n">
+      <c r="H14" s="42" t="n">
+        <v>25032</v>
+      </c>
+      <c r="I14" s="43">
+        <f>O14/F14</f>
+        <v/>
+      </c>
+      <c r="J14" s="42">
+        <f>ROUND(O14/H14,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="42" t="n">
         <v>14985030</v>
       </c>
-      <c r="L14" s="41" t="n">
+      <c r="L14" s="42" t="n">
         <v>118255596</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="45">
         <f>L14/K14</f>
         <v/>
       </c>
@@ -1339,6 +1388,9 @@
 마이크로 IMC 성과 가장 잘 워킹하는 브랜드</t>
         </is>
       </c>
+      <c r="O14" s="44" t="n">
+        <v>57426917</v>
+      </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" s="35">
       <c r="B15" s="13" t="inlineStr">
@@ -1346,36 +1398,38 @@
           <t>웨이크메이크</t>
         </is>
       </c>
-      <c r="C15" s="41" t="n">
+      <c r="C15" s="42" t="n">
         <v>70</v>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D15" s="42" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="42">
         <f>SUM(C15:D15)</f>
         <v/>
       </c>
-      <c r="F15" s="41" t="n">
+      <c r="F15" s="42" t="n">
         <v>3143931</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="42">
         <f>F15/E15</f>
         <v/>
       </c>
-      <c r="H15" s="41" t="n">
-        <v>18097</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="J15" s="41" t="n">
-        <v>2147</v>
-      </c>
-      <c r="K15" s="41" t="n">
+      <c r="H15" s="42" t="n">
+        <v>19540</v>
+      </c>
+      <c r="I15" s="43">
+        <f>O15/F15</f>
+        <v/>
+      </c>
+      <c r="J15" s="42">
+        <f>ROUND(O15/H15,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="42" t="n">
         <v>16409851</v>
       </c>
-      <c r="L15" s="41" t="n">
+      <c r="L15" s="42" t="n">
         <v>113788050</v>
       </c>
       <c r="M15" s="15">
@@ -1388,6 +1442,9 @@
 UGC 협업 수량 증대해도 좋을 것으로 판단</t>
         </is>
       </c>
+      <c r="O15" s="44" t="n">
+        <v>68676009</v>
+      </c>
     </row>
     <row r="16" ht="39.6" customHeight="1" s="35">
       <c r="B16" s="13" t="inlineStr">
@@ -1395,39 +1452,41 @@
           <t>루테카</t>
         </is>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C16" s="42" t="n">
         <v>124</v>
       </c>
-      <c r="D16" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="41">
+      <c r="D16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="42">
         <f>SUM(C16:D16)</f>
         <v/>
       </c>
-      <c r="F16" s="41" t="n">
+      <c r="F16" s="42" t="n">
         <v>1655285</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="42">
         <f>F16/E16</f>
         <v/>
       </c>
-      <c r="H16" s="41" t="n">
-        <v>9444</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="J16" s="41" t="n">
-        <v>2382</v>
-      </c>
-      <c r="K16" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="43" t="inlineStr">
+      <c r="H16" s="42" t="n">
+        <v>14046</v>
+      </c>
+      <c r="I16" s="43">
+        <f>O16/F16</f>
+        <v/>
+      </c>
+      <c r="J16" s="42">
+        <f>ROUND(O16/H16,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1438,6 +1497,9 @@
 (브랜드 fade out)</t>
         </is>
       </c>
+      <c r="O16" s="44" t="n">
+        <v>39769333</v>
+      </c>
     </row>
     <row r="17" ht="39.6" customHeight="1" s="35">
       <c r="B17" s="13" t="inlineStr">
@@ -1445,36 +1507,38 @@
           <t>컬러그램</t>
         </is>
       </c>
-      <c r="C17" s="41" t="n">
+      <c r="C17" s="42" t="n">
         <v>45</v>
       </c>
-      <c r="D17" s="41" t="n">
+      <c r="D17" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>SUM(C17:D17)</f>
         <v/>
       </c>
-      <c r="F17" s="41" t="n">
+      <c r="F17" s="42" t="n">
         <v>1583237</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <f>F17/E17</f>
         <v/>
       </c>
-      <c r="H17" s="41" t="n">
-        <v>8511</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="J17" s="41" t="n">
-        <v>3812</v>
-      </c>
-      <c r="K17" s="41" t="n">
+      <c r="H17" s="42" t="n">
+        <v>10780</v>
+      </c>
+      <c r="I17" s="43">
+        <f>O17/F17</f>
+        <v/>
+      </c>
+      <c r="J17" s="42">
+        <f>ROUND(O17/H17,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="42" t="n">
         <v>7670607</v>
       </c>
-      <c r="L17" s="41" t="n">
+      <c r="L17" s="42" t="n">
         <v>61405809</v>
       </c>
       <c r="M17" s="15">
@@ -1487,6 +1551,9 @@
 → 협업 수량 증가 필요</t>
         </is>
       </c>
+      <c r="O17" s="44" t="n">
+        <v>57352548</v>
+      </c>
     </row>
     <row r="18" ht="39.6" customHeight="1" s="35">
       <c r="B18" s="13" t="inlineStr">
@@ -1494,39 +1561,41 @@
           <t>케어플러스</t>
         </is>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="41">
+      <c r="D18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="42">
         <f>SUM(C18:D18)</f>
         <v/>
       </c>
-      <c r="F18" s="41" t="n">
+      <c r="F18" s="42" t="n">
         <v>188488</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="42">
         <f>F18/E18</f>
         <v/>
       </c>
-      <c r="H18" s="41" t="n">
+      <c r="H18" s="42" t="n">
         <v>1839</v>
       </c>
-      <c r="I18" s="42" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="J18" s="41" t="n">
-        <v>2012</v>
-      </c>
-      <c r="K18" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="43" t="inlineStr">
+      <c r="I18" s="43">
+        <f>O18/F18</f>
+        <v/>
+      </c>
+      <c r="J18" s="42">
+        <f>ROUND(O18/H18,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1537,6 +1606,9 @@
 원고료 마이크로 5건×20만 + 나노 27건×10만</t>
         </is>
       </c>
+      <c r="O18" s="44" t="n">
+        <v>6539846</v>
+      </c>
     </row>
     <row r="19" ht="39.6" customHeight="1" s="35">
       <c r="B19" s="13" t="inlineStr">
@@ -1544,48 +1616,53 @@
           <t>필리밀리</t>
         </is>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="42" t="n">
         <v>27</v>
       </c>
-      <c r="D19" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="41">
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42">
         <f>SUM(C19:D19)</f>
         <v/>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F19" s="42" t="n">
         <v>1353401</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="42">
         <f>F19/E19</f>
         <v/>
       </c>
-      <c r="H19" s="41" t="n">
-        <v>1967</v>
-      </c>
-      <c r="I19" s="42" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="J19" s="41" t="n">
-        <v>3203</v>
-      </c>
-      <c r="K19" s="41" t="n">
+      <c r="H19" s="42" t="n">
+        <v>2409</v>
+      </c>
+      <c r="I19" s="43">
+        <f>O19/F19</f>
+        <v/>
+      </c>
+      <c r="J19" s="42">
+        <f>ROUND(O19/H19,0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="42" t="n">
         <v>14086284</v>
       </c>
-      <c r="L19" s="41" t="n">
+      <c r="L19" s="42" t="n">
         <v>121998372</v>
       </c>
       <c r="M19" s="15">
         <f>L19/K19</f>
         <v/>
       </c>
-      <c r="N19" s="44" t="inlineStr">
+      <c r="N19" s="46" t="inlineStr">
         <is>
           <t>전체 브랜드 중 ROAS 1위
 최저 CPA 확보</t>
         </is>
       </c>
+      <c r="O19" s="44" t="n">
+        <v>11135413</v>
+      </c>
     </row>
     <row r="20" ht="26.4" customHeight="1" s="35">
       <c r="B20" s="13" t="inlineStr">
@@ -1593,39 +1670,41 @@
           <t>올더베러</t>
         </is>
       </c>
-      <c r="C20" s="45" t="n">
+      <c r="C20" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="45">
+      <c r="D20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="47">
         <f>SUM(C20:D20)</f>
         <v/>
       </c>
-      <c r="F20" s="45" t="n">
+      <c r="F20" s="47" t="n">
         <v>396952</v>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="47">
         <f>F20/E20</f>
         <v/>
       </c>
-      <c r="H20" s="45" t="n">
+      <c r="H20" s="47" t="n">
         <v>3440</v>
       </c>
-      <c r="I20" s="46" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="J20" s="45" t="n">
-        <v>581</v>
-      </c>
-      <c r="K20" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="47" t="inlineStr">
+      <c r="I20" s="48">
+        <f>O20/F20</f>
+        <v/>
+      </c>
+      <c r="J20" s="47">
+        <f>ROUND(O20/H20,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1634,6 +1713,9 @@
         <is>
           <t>퍼포먼스 광고 미집행</t>
         </is>
+      </c>
+      <c r="O20" s="44" t="n">
+        <v>3535052</v>
       </c>
     </row>
     <row r="21" ht="26.4" customHeight="1" s="35">
@@ -1642,86 +1724,99 @@
           <t>소계</t>
         </is>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="50">
         <f>SUM(C8:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="50">
         <f>SUM(D8:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="50">
         <f>SUM(E8:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="50">
         <f>SUM(F8:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="50">
         <f>F21/E21</f>
         <v/>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="50">
         <f>SUM(H8:H20)</f>
         <v/>
       </c>
-      <c r="I21" s="49" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J21" s="48" t="n">
-        <v>1261</v>
-      </c>
-      <c r="K21" s="48">
+      <c r="I21" s="51">
+        <f>O21/F21</f>
+        <v/>
+      </c>
+      <c r="J21" s="50">
+        <f>ROUND(O21/H21,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="50">
         <f>SUM(K8:K20)</f>
         <v/>
       </c>
-      <c r="L21" s="48">
+      <c r="L21" s="50">
         <f>SUM(L8:L20)</f>
         <v/>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="52">
         <f>L21/K21</f>
         <v/>
       </c>
-      <c r="N21" s="51" t="inlineStr">
+      <c r="N21" s="53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="O21" s="54">
+        <f>SUM(O8:O20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>※ 참여수 = 좋아요 + 댓글 / 평균 CPV = 크리에이터 원고료 ÷ 조회수 / 평균 CPE = 크리에이터 원고료 ÷ 참여수</t>
+          <t>※ 비용 = 세금계산서 발행 확정 900,344,264원 (26.02~08 확정 840,514,264 + 25년 발행 59,830,000 · 바이오힐보 US 30,000,000 포함). + JP 미발행 8,904,000 → 진행 기준 909,248,264원</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>※ 소계 CPV·CPE = 크리에이터 원고료 492,408,205원 ÷ 조회수 56,612,765 / 참여 390,370 (표준 기준 ⑤) → CPV 8.70원 · CPE 1,261원. 바이오힐보 US 행은 원고료 미기재로 청구액 30,000,000원 기준이라 브랜드 행 단순 합과 소계가 일치하지 않는다.</t>
+          <t>※ 브랜드별 세금계산서는 발행 총액을 원고료 비율로 안분한 값이다(바이오힐보 US는 실제 청구 30,000,000원 직접 계상). 발행 내역상 브랜드 귀속 미확정 조정액이 있어 안분 처리했다.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>※ 세금계산서 기준으로 보면 900,344,264원 ÷ 조회수 56,612,765 = CPV 15.90원 / ÷ 참여 390,370 = CPE 2,306원. 원고료는 마크업·VAT 제외 금액으로 청구액의 54.7%다.</t>
+          <t>※ 평균 CPV = 세금계산서 ÷ 조회수 / 평균 CPE = 세금계산서 ÷ 참여수 / 참여수 = 좋아요 + 댓글 → 소계 CPV 15.90원 · CPE 1,922원 · 건당 청구액 420,918원</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>※ 세금계산서 발행 확정 총액 900,344,264원 = 26.02~08 확정 840,514,264 + 25년 발행 59,830,000(바이오힐보 US 30,000,000 포함). + JP 미발행 8,904,000 → 진행 기준 909,248,264원.</t>
+          <t>※ 참여수는 좋아요 데이터 공란 505건(IMD 2,050건의 24.6%)을 브랜드·국가별 좋아요율과 좋아요/댓글비의 중앙값으로 추정해 반영한 값이다 — 좋아요 실측 358,615 + 추정 78,128 = 436,743, 댓글 31,755(전량 실측)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>※ 좋아요 데이터 공란 505건(24.6%) 보정 시 참여 469,050 · 참여율 0.83% · CPE 1,050원(원고료)/1,920원(청구). 위 표는 미보정 공식 수치다.</t>
+          <t>※ 미집계 53건(바이오힐보 US 32 + 웨이크메이크JP 26.09 21)은 조회수·참여 데이터가 없어 성과 분모에서 제외했다. 수량·비용에는 포함되어 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>※ (참고) 크리에이터 원고료 492,408,205원 = 청구액의 54.7%. 마크업·VAT·솔루션·지급대행 제외 금액으로 위 단가 산정에는 사용하지 않았다.</t>
         </is>
       </c>
     </row>

--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN.xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_260907 HAN.xlsx
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O27"/>
+  <dimension ref="B2:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.796875" customWidth="1" style="3" min="1" max="1"/>
@@ -860,7 +860,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ 통계 : 25.04 ~ 26.09 · 국내외 전체 2,139건(글로벌 167건 = JP 99 + US 68) · 26.09.07 기준</t>
+          <t>※ 통계 : 25.04 ~ 26.09 · 국내외 전체 2,165건(글로벌 167건 = JP 99 + US 68) · 26.09.07 기준</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -879,7 +879,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>※ RD : 표준 기준 ⑤ — 수량·비용 전체 2,139건 / 조회수·참여 성과 집계분 2,086건 · 모든 단가는 세금계산서 발행 비용 기준</t>
+          <t>※ RD : 표준 기준 ⑤ — 수량·비용 전체 2,165건 / 조회수·참여 성과 집계분 2,112건 · 모든 단가는 세금계산서 발행 비용 기준</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="O8" s="44" t="n">
-        <v>329997090</v>
+        <v>325861024</v>
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" s="35">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="O9" s="44" t="n">
-        <v>117186968</v>
+        <v>115718190</v>
       </c>
     </row>
     <row r="10" ht="26.4" customHeight="1" s="35">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="O10" s="44" t="n">
-        <v>108791220</v>
+        <v>107427671</v>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="35">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="O11" s="44" t="n">
-        <v>66989232</v>
+        <v>66149614</v>
       </c>
     </row>
     <row r="12" ht="39.6" customHeight="1" s="35">
@@ -1252,7 +1252,7 @@
         <v/>
       </c>
       <c r="H12" s="42" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I12" s="43">
         <f>O12/F12</f>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="O12" s="44" t="n">
-        <v>2944636</v>
+        <v>2907729</v>
       </c>
     </row>
     <row r="13" ht="39.6" customHeight="1" s="35">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="O14" s="44" t="n">
-        <v>57426917</v>
+        <v>56707149</v>
       </c>
     </row>
     <row r="15" ht="39.6" customHeight="1" s="35">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="O15" s="44" t="n">
-        <v>68676009</v>
+        <v>67815249</v>
       </c>
     </row>
     <row r="16" ht="39.6" customHeight="1" s="35">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="O16" s="44" t="n">
-        <v>39769333</v>
+        <v>39270879</v>
       </c>
     </row>
     <row r="17" ht="39.6" customHeight="1" s="35">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D17" s="42" t="n">
         <v>32</v>
@@ -1518,14 +1518,14 @@
         <v/>
       </c>
       <c r="F17" s="42" t="n">
-        <v>1583237</v>
+        <v>2653321</v>
       </c>
       <c r="G17" s="42">
         <f>F17/E17</f>
         <v/>
       </c>
       <c r="H17" s="42" t="n">
-        <v>10780</v>
+        <v>14526</v>
       </c>
       <c r="I17" s="43">
         <f>O17/F17</f>
@@ -1536,10 +1536,10 @@
         <v/>
       </c>
       <c r="K17" s="42" t="n">
-        <v>7670607</v>
+        <v>23514230</v>
       </c>
       <c r="L17" s="42" t="n">
-        <v>61405809</v>
+        <v>134432958</v>
       </c>
       <c r="M17" s="15">
         <f>L17/K17</f>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="N17" s="16" t="inlineStr">
         <is>
-          <t>전체 브랜드 중 ROAS 2위(800% 이상)
-→ 협업 수량 증가 필요</t>
+          <t>IMD 26.09.07로 103건 확정(v8 77건 → +26)
+조회수 +68% · 광고비 3.1배 · 매출 2.2배</t>
         </is>
       </c>
       <c r="O17" s="44" t="n">
-        <v>57352548</v>
+        <v>67542290</v>
       </c>
     </row>
     <row r="18" ht="39.6" customHeight="1" s="35">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="O18" s="44" t="n">
-        <v>6539846</v>
+        <v>6457878</v>
       </c>
     </row>
     <row r="19" ht="39.6" customHeight="1" s="35">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="O19" s="44" t="n">
-        <v>11135413</v>
+        <v>10995846</v>
       </c>
     </row>
     <row r="20" ht="26.4" customHeight="1" s="35">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="O20" s="44" t="n">
-        <v>3535052</v>
+        <v>3490745</v>
       </c>
     </row>
     <row r="21" ht="26.4" customHeight="1" s="35">
@@ -1795,14 +1795,14 @@
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>※ 평균 CPV = 세금계산서 ÷ 조회수 / 평균 CPE = 세금계산서 ÷ 참여수 / 참여수 = 좋아요 + 댓글 → 소계 CPV 15.90원 · CPE 1,922원 · 건당 청구액 420,918원</t>
+          <t>※ 평균 CPV = 세금계산서 ÷ 조회수 / 평균 CPE = 세금계산서 ÷ 참여수 / 참여수 = 좋아요 + 댓글 → 소계 CPV 15.61원 · CPE 1,907원 · 건당 청구액 415,863원</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>※ 참여수는 좋아요 데이터 공란 505건(IMD 2,050건의 24.6%)을 브랜드·국가별 좋아요율과 좋아요/댓글비의 중앙값으로 추정해 반영한 값이다 — 좋아요 실측 358,615 + 추정 78,128 = 436,743, 댓글 31,755(전량 실측)</t>
+          <t>※ 참여수는 좋아요 데이터 공란 519건(IMD 2,076건의 25.0%)을 브랜드·국가별 좋아요율과 좋아요/댓글비의 중앙값으로 추정해 반영한 값이다 — 좋아요 실측 359,877 + 추정 80,292 = 440,169, 댓글 32,083(전량 실측)</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,14 @@
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>※ (참고) 크리에이터 원고료 492,408,205원 = 청구액의 54.7%. 마크업·VAT·솔루션·지급대행 제외 금액으로 위 단가 산정에는 사용하지 않았다.</t>
+          <t>※ (참고) 크리에이터 원고료 498,658,205원 = 청구액의 55.4%. 마크업·VAT·솔루션·지급대행 제외 금액으로 위 단가 산정에는 사용하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>※ 컬러그램은 IMD 26.09.07 최신본으로 103건 확정(v8 77건은 부분집합, URL 대조 확인). 다른 브랜드도 동일 누락 가능성이 있어 최신 IMD 확인이 필요하다.</t>
         </is>
       </c>
     </row>
